--- a/output/observations-summary.xlsx
+++ b/output/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="29">
   <si>
     <t>Profile</t>
   </si>
@@ -53,6 +53,9 @@
     <t>Botswana AMR Gram Stain Observation</t>
   </si>
   <si>
+    <t>null#laboratory, null#18725-2</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -75,6 +78,27 @@
   </si>
   <si>
     <t>LOINC#634-6</t>
+  </si>
+  <si>
+    <t>botswana-amr-special-test-observation</t>
+  </si>
+  <si>
+    <t>Botswana AMR Special Test Observation</t>
+  </si>
+  <si>
+    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/ValueSet/botswana-amr-special-test-vs (required)</t>
+  </si>
+  <si>
+    <t>botswana-amr-susceptibility-observation</t>
+  </si>
+  <si>
+    <t>Botswana AMR Susceptibility Observation</t>
+  </si>
+  <si>
+    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/ValueSet/botswana-amr-antibiotic-susceptibility-loinc (required)</t>
+  </si>
+  <si>
+    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
   </si>
 </sst>
 </file>
@@ -208,7 +232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -257,63 +281,133 @@
         <v>13</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>13</v>
       </c>
       <c r="D3" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K3" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="E3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s" s="2">
+      <c r="D4" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K4" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="G3" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s" s="2">
+      <c r="D5" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s" s="2">
         <v>16</v>
       </c>
-      <c r="I3" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K3" t="s" s="2">
-        <v>13</v>
+      <c r="H5" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="I5" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K5" t="s" s="2">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/output/observations-summary.xlsx
+++ b/output/observations-summary.xlsx
@@ -86,7 +86,7 @@
     <t>Botswana AMR Special Test Observation</t>
   </si>
   <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/ValueSet/botswana-amr-special-test-vs (required)</t>
+    <t>http://bw.health.gov/fhir/amr/ValueSet/botswana-amr-special-test-vs (required)</t>
   </si>
   <si>
     <t>botswana-amr-susceptibility-observation</t>
@@ -95,7 +95,7 @@
     <t>Botswana AMR Susceptibility Observation</t>
   </si>
   <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/ValueSet/botswana-amr-antibiotic-susceptibility-loinc (required)</t>
+    <t>http://bw.health.gov/fhir/amr/ValueSet/botswana-amr-antibiotic-susceptibility-loinc (required)</t>
   </si>
   <si>
     <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
